--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488225_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488225_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.769</v>
+        <v>5.4752</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9757</v>
+        <v>5.6819</v>
       </c>
       <c r="F2" t="n">
         <v>-0.2067</v>
@@ -610,10 +610,10 @@
         <v>1.1117</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6106</v>
+        <v>0.3168</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9314</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="U2" t="n">
         <v>-0.3209</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1913</v>
+        <v>3.2773</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0143</v>
+        <v>3.9278</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8229</v>
+        <v>-0.6506</v>
       </c>
       <c r="G3" t="n">
         <v>1.1197</v>
@@ -688,13 +688,13 @@
         <v>2.2234</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6248</v>
+        <v>0.7107</v>
       </c>
       <c r="T3" t="n">
-        <v>1.016</v>
+        <v>0.9296</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3912</v>
+        <v>-0.2189</v>
       </c>
       <c r="V3" t="n">
         <v>1.4469</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0636</v>
+        <v>0.755</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0686</v>
+        <v>1.0801</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0049</v>
+        <v>-0.325</v>
       </c>
       <c r="G5" t="n">
         <v>-3.9387</v>
@@ -844,13 +844,13 @@
         <v>2.0382</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5549</v>
+        <v>1.2463</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9824000000000001</v>
+        <v>0.9939</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5725</v>
+        <v>0.2524</v>
       </c>
       <c r="V5" t="n">
         <v>2.7063</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. HEPBURN</t>
+          <t>J. REYES BARRANCO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4381</v>
+        <v>0.6284</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0641</v>
+        <v>2.6085</v>
       </c>
       <c r="F6" t="n">
-        <v>0.374</v>
+        <v>-1.9801</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3505</v>
+        <v>-1.8415</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2199</v>
+        <v>-1.2117</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1306</v>
+        <v>-0.6299</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0429</v>
+        <v>0.9337</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0429</v>
+        <v>0.2275</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.7063</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3076</v>
+        <v>-2.7752</v>
       </c>
       <c r="N6" t="n">
-        <v>0.177</v>
+        <v>-1.4391</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1306</v>
+        <v>-1.3361</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3706</v>
+        <v>0.7411</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3706</v>
+        <v>1.6676</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.283</v>
+        <v>0.7844</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0211</v>
+        <v>0.7135</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3042</v>
+        <v>0.0709</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.9444</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.8877</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.9433</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. REYES BARRANCO</t>
+          <t>P. HEPBURN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1676</v>
+        <v>0.4873</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0094</v>
+        <v>0.0641</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1771</v>
+        <v>0.4232</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8415</v>
+        <v>0.3505</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2117</v>
+        <v>0.2199</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6299</v>
+        <v>0.1306</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9337</v>
+        <v>0.0429</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2275</v>
+        <v>0.0429</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7063</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.7752</v>
+        <v>0.3076</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4391</v>
+        <v>0.177</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3361</v>
+        <v>0.1306</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7411</v>
+        <v>0.3706</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6676</v>
+        <v>0.3706</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0117</v>
+        <v>-0.2338</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1144</v>
+        <v>0.0211</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1261</v>
+        <v>-0.2549</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9444</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8877</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9433</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0166</v>
+        <v>-2.6374</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1695</v>
+        <v>1.4748</v>
       </c>
       <c r="F8" t="n">
-        <v>-4.186</v>
+        <v>-4.1122</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5206</v>
@@ -1078,13 +1078,13 @@
         <v>0.9264</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.09379999999999999</v>
+        <v>0.2854</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1057</v>
+        <v>0.411</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1995</v>
+        <v>-0.1256</v>
       </c>
       <c r="V8" t="n">
         <v>-2.958</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>M. KOZAR SIMIONIKA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.7076</v>
+        <v>-3.7012</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6132</v>
+        <v>-1.354</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0944</v>
+        <v>-2.3472</v>
       </c>
       <c r="G9" t="n">
-        <v>-6.6564</v>
+        <v>-1.0474</v>
       </c>
       <c r="H9" t="n">
-        <v>-5.6935</v>
+        <v>-0.9123</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9629</v>
+        <v>-0.1351</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.1299</v>
+        <v>-1.1784</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.265</v>
+        <v>-1.2198</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1351</v>
+        <v>0.0415</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.5265</v>
+        <v>0.131</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.4285</v>
+        <v>0.3076</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.098</v>
+        <v>-0.1766</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1499</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4087</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5565</v>
+        <v>-0.4517</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7783</v>
+        <v>-0.1756</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7782</v>
+        <v>-0.2761</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1335</v>
+        <v>-2.2022</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8883</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7548</v>
+        <v>-2.2022</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. KOZAR SIMIONIKA</t>
+          <t>A. GALLEGO GOMEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9469</v>
+        <v>-3.8206</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4519</v>
+        <v>-3.6174</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.495</v>
+        <v>-0.2032</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0474</v>
+        <v>-0.5581</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9123</v>
+        <v>1.0823</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1351</v>
+        <v>-1.6404</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.1784</v>
+        <v>-0.6375999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2198</v>
+        <v>1.2796</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0415</v>
+        <v>-1.9171</v>
       </c>
       <c r="M10" t="n">
-        <v>0.131</v>
+        <v>0.0795</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3076</v>
+        <v>-0.1973</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1766</v>
+        <v>0.2767</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6974</v>
+        <v>-0.5214</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2736</v>
+        <v>-0.2005</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4238</v>
+        <v>-0.3209</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.2022</v>
+        <v>-1.2589</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.2022</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. GALLEGO GOMEZ</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5072</v>
+        <v>-4.8007</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.107</v>
+        <v>-3.1893</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4002</v>
+        <v>-1.6114</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5581</v>
+        <v>-6.6564</v>
       </c>
       <c r="H11" t="n">
-        <v>1.0823</v>
+        <v>-5.6935</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6404</v>
+        <v>-0.9629</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-3.1299</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2796</v>
+        <v>-3.265</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9171</v>
+        <v>0.1351</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0795</v>
+        <v>-3.5265</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1973</v>
+        <v>-2.4285</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2767</v>
+        <v>-1.098</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.4823</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.7793</v>
+        <v>-3.1499</v>
       </c>
       <c r="R11" t="n">
-        <v>1.297</v>
+        <v>2.4087</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.208</v>
+        <v>1.4633</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6901</v>
+        <v>1.2022</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5178</v>
+        <v>0.2611</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2589</v>
+        <v>1.1335</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.8883</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2589</v>
+        <v>-0.7548</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.951499999999999</v>
+        <v>-2.4043</v>
       </c>
       <c r="E12" t="n">
-        <v>8.061899999999998</v>
+        <v>8.6089</v>
       </c>
       <c r="F12" t="n">
         <v>-11.0132</v>
@@ -1357,7 +1357,7 @@
         <v>-10.4115</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.919499999999999</v>
+        <v>-5.919500000000001</v>
       </c>
       <c r="I12" t="n">
         <v>-4.4922</v>
@@ -1375,13 +1375,13 @@
         <v>-13.9453</v>
       </c>
       <c r="N12" t="n">
-        <v>-8.225499999999998</v>
+        <v>-8.2255</v>
       </c>
       <c r="O12" t="n">
         <v>-5.7199</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-1.110223024625157e-16</v>
       </c>
       <c r="Q12" t="n">
         <v>-12.0436</v>
@@ -1390,13 +1390,13 @@
         <v>12.0436</v>
       </c>
       <c r="S12" t="n">
-        <v>3.0529</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>3.9856</v>
+        <v>4.5328</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9328000000000001</v>
+        <v>-0.9329</v>
       </c>
       <c r="V12" t="n">
         <v>4.407100000000001</v>
@@ -1405,7 +1405,7 @@
         <v>12.5858</v>
       </c>
       <c r="X12" t="n">
-        <v>-8.178700000000001</v>
+        <v>-8.178699999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6198</v>
+        <v>4.9365</v>
       </c>
       <c r="E13" t="n">
-        <v>3.855</v>
+        <v>4.0509</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7648</v>
+        <v>0.8857</v>
       </c>
       <c r="G13" t="n">
         <v>3.6285</v>
@@ -1468,13 +1468,13 @@
         <v>1.8529</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.061</v>
+        <v>-0.7443</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.475</v>
+        <v>-0.2791</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.586</v>
+        <v>-0.4651</v>
       </c>
       <c r="V13" t="n">
         <v>4.0904</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2251</v>
+        <v>3.7825</v>
       </c>
       <c r="E14" t="n">
-        <v>5.8876</v>
+        <v>5.3979</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6624</v>
+        <v>-1.6154</v>
       </c>
       <c r="G14" t="n">
         <v>2.8113</v>
@@ -1546,13 +1546,13 @@
         <v>2.4087</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4143</v>
+        <v>-0.0283</v>
       </c>
       <c r="T14" t="n">
-        <v>0.776</v>
+        <v>0.2864</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3617</v>
+        <v>-0.3146</v>
       </c>
       <c r="V14" t="n">
         <v>0.6289</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3356</v>
+        <v>3.3486</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9169</v>
+        <v>2.6024</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4186</v>
+        <v>0.7462</v>
       </c>
       <c r="G15" t="n">
         <v>-0.5732</v>
@@ -1624,13 +1624,13 @@
         <v>1.8529</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.591</v>
+        <v>-0.5779</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8754</v>
+        <v>-0.1899</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7155</v>
+        <v>-0.388</v>
       </c>
       <c r="V15" t="n">
         <v>2.8321</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7925</v>
+        <v>1.8874</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0917</v>
+        <v>0.4959</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8842</v>
+        <v>1.3915</v>
       </c>
       <c r="G17" t="n">
         <v>1.1078</v>
@@ -1780,13 +1780,13 @@
         <v>2.0382</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4276</v>
+        <v>-0.3326</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5508999999999999</v>
+        <v>0.0367</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8767</v>
+        <v>-0.3694</v>
       </c>
       <c r="V17" t="n">
         <v>0.0005</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6903</v>
+        <v>0.2751</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3327</v>
+        <v>-0.2549</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3576</v>
+        <v>0.53</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1409</v>
@@ -1858,13 +1858,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4606</v>
+        <v>0.0454</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9986</v>
+        <v>0.411</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.538</v>
+        <v>-0.3656</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9685</v>
+        <v>-0.5928</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2189</v>
+        <v>-0.023</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7496</v>
+        <v>-0.5698</v>
       </c>
       <c r="G19" t="n">
         <v>-0.023</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3166</v>
+        <v>0.0591</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2189</v>
+        <v>-0.023</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0977</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6289</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2824</v>
+        <v>-2.2172</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8302</v>
+        <v>0.6344</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1127</v>
+        <v>-2.8515</v>
       </c>
       <c r="G20" t="n">
         <v>0.7575</v>
@@ -2014,13 +2014,13 @@
         <v>0.7411</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.337</v>
+        <v>-0.2717</v>
       </c>
       <c r="T20" t="n">
-        <v>0.051</v>
+        <v>-0.1449</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.388</v>
+        <v>-0.1269</v>
       </c>
       <c r="V20" t="n">
         <v>-2.5177</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. GALIANO AVILA</t>
+          <t>J. SANCHEZ BARQUIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4014</v>
+        <v>-2.2906</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.188</v>
+        <v>0.7386</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2134</v>
+        <v>-3.0292</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.445</v>
+        <v>2.0416</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6248</v>
+        <v>-0.9505</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1798</v>
+        <v>2.9921</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.495</v>
+        <v>2.4214</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.7439</v>
+        <v>-0.202</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2488</v>
+        <v>2.6234</v>
       </c>
       <c r="M21" t="n">
-        <v>0.05</v>
+        <v>-0.3798</v>
       </c>
       <c r="N21" t="n">
-        <v>0.119</v>
+        <v>-0.7485000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.3687</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5558999999999999</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1117</v>
+        <v>-1.8529</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6676</v>
+        <v>0.3706</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6904</v>
+        <v>-0.0177</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1043</v>
+        <v>0.1701</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4139</v>
+        <v>-0.1878</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.2027</v>
+        <v>-2.8321</v>
       </c>
       <c r="W21" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.5172</v>
+        <v>-2.8321</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. SANCHEZ BARQUIN</t>
+          <t>S. GALIANO AVILA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8959</v>
+        <v>-3.0623</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6407</v>
+        <v>-1.8735</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.5365</v>
+        <v>-1.1888</v>
       </c>
       <c r="G22" t="n">
-        <v>2.0416</v>
+        <v>-1.445</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9505</v>
+        <v>-1.6248</v>
       </c>
       <c r="I22" t="n">
-        <v>2.9921</v>
+        <v>0.1798</v>
       </c>
       <c r="J22" t="n">
-        <v>2.4214</v>
+        <v>-1.495</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.202</v>
+        <v>-1.7439</v>
       </c>
       <c r="L22" t="n">
-        <v>2.6234</v>
+        <v>0.2488</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3798</v>
+        <v>0.05</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7485000000000001</v>
+        <v>0.119</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3687</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.4823</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8529</v>
+        <v>-1.1117</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3706</v>
+        <v>1.6676</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.623</v>
+        <v>0.0295</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0721</v>
+        <v>0.4188</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6951000000000001</v>
+        <v>-0.3892</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.8321</v>
+        <v>-2.2027</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.8321</v>
+        <v>-2.5172</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3518</v>
+        <v>-3.3455</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5095</v>
+        <v>-2.3136</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8423</v>
+        <v>-1.0318</v>
       </c>
       <c r="G23" t="n">
         <v>0.0585</v>
@@ -2248,13 +2248,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7379</v>
+        <v>0.7443</v>
       </c>
       <c r="T23" t="n">
-        <v>0.051</v>
+        <v>0.2469</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6869</v>
+        <v>0.4974</v>
       </c>
       <c r="V23" t="n">
         <v>-3.7777</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.951599999999997</v>
+        <v>4.91</v>
       </c>
       <c r="E24" t="n">
-        <v>11.6433</v>
+        <v>11.6434</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.691700000000001</v>
+        <v>-6.7331</v>
       </c>
       <c r="G24" t="n">
         <v>10.4114</v>
@@ -2308,7 +2308,7 @@
         <v>5.719900000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.534</v>
+        <v>-3.534000000000001</v>
       </c>
       <c r="N24" t="n">
         <v>-2.3062</v>
@@ -2317,7 +2317,7 @@
         <v>-1.2277</v>
       </c>
       <c r="P24" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>1.665334536937735e-16</v>
       </c>
       <c r="Q24" t="n">
         <v>-12.0436</v>
@@ -2326,13 +2326,13 @@
         <v>12.0438</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.053</v>
+        <v>-1.0942</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9328000000000002</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.9857</v>
+        <v>-2.0271</v>
       </c>
       <c r="V24" t="n">
         <v>-4.407200000000001</v>
